--- a/content/W01/D2/demos/C2_W01_D02_decision_tool_STUDENT.xlsx
+++ b/content/W01/D2/demos/C2_W01_D02_decision_tool_STUDENT.xlsx
@@ -22,7 +22,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+  </numFmts>
   <fonts count="6">
     <font>
       <name val="Calibri"/>
@@ -103,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -117,6 +119,7 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1004,14 +1007,14 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Discount recorded, total (Rs)</t>
+          <t>Orders with a discount above Rs 0</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>2400</v>
+        <v>24</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>2250</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
@@ -1037,14 +1040,14 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Per order, absent read as zero</t>
-        </is>
-      </c>
-      <c r="B11">
+          <t>Share with a discount, absent read as zero</t>
+        </is>
+      </c>
+      <c r="B11" s="9">
         <f>B7/B5</f>
         <v/>
       </c>
-      <c r="C11">
+      <c r="C11" s="9">
         <f>C7/C5</f>
         <v/>
       </c>
@@ -1052,14 +1055,14 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Per order, where recorded</t>
-        </is>
-      </c>
-      <c r="B12">
+          <t>Share with a discount, where recorded</t>
+        </is>
+      </c>
+      <c r="B12" s="9">
         <f>B7/B6</f>
         <v/>
       </c>
-      <c r="C12">
+      <c r="C12" s="9">
         <f>C7/C5</f>
         <v/>
       </c>
@@ -1067,22 +1070,37 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Share at most, every blank discounted</t>
+        </is>
+      </c>
+      <c r="B13" s="9">
+        <f>(B7+B5-B6)/B5</f>
+        <v/>
+      </c>
+      <c r="C13" s="9">
+        <f>(C7+C5-C6)/C5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>The most the branch could move (Rs)</t>
         </is>
       </c>
-      <c r="C13">
+      <c r="C14">
         <f>B8*C5</f>
         <v/>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>The check</t>
         </is>
       </c>
-      <c r="B14" s="2">
-        <f>IF(AND(ABS(B12*B6-B7)&lt;0.5,ABS(C12*C6-C7)&lt;0.5),"The where-recorded averages multiply back to the recorded totals.","A where-recorded average does not multiply back to its recorded total: it divides by every order. Fix it first.")</f>
+      <c r="B15" s="2">
+        <f>IF(AND(ABS(B12*B6-B7)&lt;0.5,ABS(C12*C6-C7)&lt;0.5),"The where-recorded shares multiply back to the orders with a discount.","A where-recorded share does not multiply back to its orders with a discount: it divides by every order. Fix it first.")</f>
         <v/>
       </c>
     </row>
@@ -1105,7 +1123,7 @@
         </is>
       </c>
       <c r="B18" s="8">
-        <f>IF(OR(ABS(B12*B6-B7)&gt;=0.5,ABS(C12*C6-C7)&gt;=0.5),"Fix the where-recorded average before choosing a default.",IF(B16="read absent as zero","Refuse the zero default: an absent discount is unknown, so the total is a floor; choose a default and write down why.",IF(B16="report where recorded","Report the discount where recorded, "&amp;IF(B12&lt;0,"-","")&amp;"Rs "&amp;IF(ROUND(ABS(B12),0)&gt;=10000000,INT(ROUND(ABS(B12),0)/10000000)&amp;","&amp;TEXT(INT(MOD(ROUND(ABS(B12),0),10000000)/100000),"00")&amp;","&amp;TEXT(INT(MOD(ROUND(ABS(B12),0),100000)/1000),"00")&amp;","&amp;TEXT(MOD(ROUND(ABS(B12),0),1000),"000"),IF(ROUND(ABS(B12),0)&gt;=100000,INT(ROUND(ABS(B12),0)/100000)&amp;","&amp;TEXT(INT(MOD(ROUND(ABS(B12),0),100000)/1000),"00")&amp;","&amp;TEXT(MOD(ROUND(ABS(B12),0),1000),"000"),IF(ROUND(ABS(B12),0)&gt;=1000,INT(ROUND(ABS(B12),0)/1000)&amp;","&amp;TEXT(MOD(ROUND(ABS(B12),0),1000),"000"),ROUND(ABS(B12),0)&amp;"")))&amp;" to "&amp;IF(C12&lt;0,"-","")&amp;"Rs "&amp;IF(ROUND(ABS(C12),0)&gt;=10000000,INT(ROUND(ABS(C12),0)/10000000)&amp;","&amp;TEXT(INT(MOD(ROUND(ABS(C12),0),10000000)/100000),"00")&amp;","&amp;TEXT(INT(MOD(ROUND(ABS(C12),0),100000)/1000),"00")&amp;","&amp;TEXT(MOD(ROUND(ABS(C12),0),1000),"000"),IF(ROUND(ABS(C12),0)&gt;=100000,INT(ROUND(ABS(C12),0)/100000)&amp;","&amp;TEXT(INT(MOD(ROUND(ABS(C12),0),100000)/1000),"00")&amp;","&amp;TEXT(MOD(ROUND(ABS(C12),0),1000),"000"),IF(ROUND(ABS(C12),0)&gt;=1000,INT(ROUND(ABS(C12),0)/1000)&amp;","&amp;TEXT(MOD(ROUND(ABS(C12),0),1000),"000"),ROUND(ABS(C12),0)&amp;"")))&amp;" an order, with the orders that lack the field reported separately.","The discount branch is at most "&amp;IF(C13&lt;0,"-","")&amp;"Rs "&amp;IF(ROUND(ABS(C13),0)&gt;=10000000,INT(ROUND(ABS(C13),0)/10000000)&amp;","&amp;TEXT(INT(MOD(ROUND(ABS(C13),0),10000000)/100000),"00")&amp;","&amp;TEXT(INT(MOD(ROUND(ABS(C13),0),100000)/1000),"00")&amp;","&amp;TEXT(MOD(ROUND(ABS(C13),0),1000),"000"),IF(ROUND(ABS(C13),0)&gt;=100000,INT(ROUND(ABS(C13),0)/100000)&amp;","&amp;TEXT(INT(MOD(ROUND(ABS(C13),0),100000)/1000),"00")&amp;","&amp;TEXT(MOD(ROUND(ABS(C13),0),1000),"000"),IF(ROUND(ABS(C13),0)&gt;=1000,INT(ROUND(ABS(C13),0)/1000)&amp;","&amp;TEXT(MOD(ROUND(ABS(C13),0),1000),"000"),ROUND(ABS(C13),0)&amp;"")))&amp;", "&amp;TEXT(100*C13/B9,"0.00")&amp;" percent of the fall, so it did not move revenue.")))</f>
+        <f>IF(OR(ABS(B12*B6-B7)&gt;=0.5,ABS(C12*C6-C7)&gt;=0.5),"Fix the where-recorded share before choosing a default.",IF(B16="read absent as zero","Refuse the zero default: an absent discount is unknown, so the share is a floor; choose a default and write down why.",IF(B16="report where recorded","Report the share where recorded, "&amp;TEXT(B12,"0.0%")&amp;" to "&amp;TEXT(C12,"0.0%")&amp;" of orders, with the orders that lack the field reported separately.","The discount branch is at most "&amp;IF(C14&lt;0,"-","")&amp;"Rs "&amp;IF(ROUND(ABS(C14),0)&gt;=10000000,INT(ROUND(ABS(C14),0)/10000000)&amp;","&amp;TEXT(INT(MOD(ROUND(ABS(C14),0),10000000)/100000),"00")&amp;","&amp;TEXT(INT(MOD(ROUND(ABS(C14),0),100000)/1000),"00")&amp;","&amp;TEXT(MOD(ROUND(ABS(C14),0),1000),"000"),IF(ROUND(ABS(C14),0)&gt;=100000,INT(ROUND(ABS(C14),0)/100000)&amp;","&amp;TEXT(INT(MOD(ROUND(ABS(C14),0),100000)/1000),"00")&amp;","&amp;TEXT(MOD(ROUND(ABS(C14),0),1000),"000"),IF(ROUND(ABS(C14),0)&gt;=1000,INT(ROUND(ABS(C14),0)/1000)&amp;","&amp;TEXT(MOD(ROUND(ABS(C14),0),1000),"000"),ROUND(ABS(C14),0)&amp;"")))&amp;", "&amp;TEXT(100*C14/B9,"0.00")&amp;" percent of the fall, so it did not move revenue.")))</f>
         <v/>
       </c>
     </row>

--- a/content/W01/D2/demos/C2_W01_D02_decision_tool_STUDENT.xlsx
+++ b/content/W01/D2/demos/C2_W01_D02_decision_tool_STUDENT.xlsx
@@ -494,7 +494,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Which branch moved: the decision tool</t>
+          <t>Which branch moved from Q1 to Q2, one decision at a time?</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Weighted or averaged?</t>
+          <t>Should the segments be weighted or averaged?</t>
         </is>
       </c>
     </row>
@@ -1394,7 +1394,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Groups in against groups out</t>
+          <t>Does every group that goes in come back out?</t>
         </is>
       </c>
     </row>
@@ -1618,7 +1618,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>The brief, assembled</t>
+          <t>Is the brief ready to go to Meera?</t>
         </is>
       </c>
     </row>

--- a/content/W01/D2/demos/C2_W01_D02_decision_tool_STUDENT.xlsx
+++ b/content/W01/D2/demos/C2_W01_D02_decision_tool_STUDENT.xlsx
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="B18" s="8">
-        <f>IF(ABS(B10*C6-B6)&gt;=1,"Fix the weekly rate that divides by the wrong weeks before comparing anything.",IF(B13="closed quarters",IF(C7=C5,"Revenue "&amp;IF(B14&lt;0,"fell ","rose ")&amp;TEXT(ABS(B14),"0.0")&amp;" percent"&amp;" between closed quarters of "&amp;C5&amp;" weeks each.","The closed quarters cover different weeks: compare a rate per week."),IF(B13="rate per week","Per week, revenue "&amp;IF(B16&lt;0,"fell ","rose ")&amp;TEXT(ABS(B16),"0.0")&amp;" percent"&amp;" on the cut window.",IF(C6&lt;&gt;C5,"Refuse the comparison: "&amp;C6&amp;" weeks against "&amp;C5&amp;" reads as "&amp;TEXT(ABS(B15),"0.0")&amp;" percent; close the window or use a rate per week.","Revenue "&amp;IF(B15&lt;0,"fell ","rose ")&amp;TEXT(ABS(B15),"0.0")&amp;" percent"&amp;" on matched weeks."))))</f>
+        <f>IF(ABS(B10*C6-B6)&gt;=1,"Fix the weekly rate that divides by the wrong weeks before comparing anything.",IF(B13="closed quarters",IF(C7=C5,"Revenue "&amp;IF(B14&lt;0,"fell ","rose ")&amp;TEXT(ABS(B14),"0.0")&amp;" percent"&amp;" between closed quarters of "&amp;C5&amp;" weeks each.","The closed quarters cover different weeks: compare a rate per week."),IF(B13="rate per week","Per week, revenue "&amp;IF(B16&lt;0,"fell ","rose ")&amp;TEXT(ABS(B16),"0.0")&amp;" percent"&amp;" on the cut window; the rate fixes the length, so send the same weeks of both beside it.",IF(C6&lt;&gt;C5,"Refuse the comparison: "&amp;C6&amp;" weeks against "&amp;C5&amp;" reads as "&amp;TEXT(ABS(B15),"0.0")&amp;" percent; compare the same weeks of both, with a rate per week beside them.","Revenue "&amp;IF(B15&lt;0,"fell ","rose ")&amp;TEXT(ABS(B15),"0.0")&amp;" percent"&amp;" on matched weeks."))))</f>
         <v/>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>The change in orders per customer for every segment, with big moves flagged in their own column rather than dropped.</t>
+          <t>The change in orders per customer for every segment, with big moves flagged in their own column and every segment kept.</t>
         </is>
       </c>
     </row>

--- a/content/W01/D2/demos/C2_W01_D02_decision_tool_STUDENT.xlsx
+++ b/content/W01/D2/demos/C2_W01_D02_decision_tool_STUDENT.xlsx
@@ -577,7 +577,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Two quarters are compared only when they cover the same weeks, or as a rate per week.</t>
+          <t>Two quarters are compared only when they cover the same weeks, with any rate per week stated beside them.</t>
         </is>
       </c>
     </row>

--- a/content/W01/D2/demos/C2_W01_D02_decision_tool_STUDENT.xlsx
+++ b/content/W01/D2/demos/C2_W01_D02_decision_tool_STUDENT.xlsx
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="B18" s="8">
-        <f>IF(ABS(B10*C6-B6)&gt;=1,"Fix the weekly rate that divides by the wrong weeks before comparing anything.",IF(B13="closed quarters",IF(C7=C5,"Revenue "&amp;IF(B14&lt;0,"fell ","rose ")&amp;TEXT(ABS(B14),"0.0")&amp;" percent"&amp;" between closed quarters of "&amp;C5&amp;" weeks each.","The closed quarters cover different weeks: compare a rate per week."),IF(B13="rate per week","Per week, revenue "&amp;IF(B16&lt;0,"fell ","rose ")&amp;TEXT(ABS(B16),"0.0")&amp;" percent"&amp;" on the cut window; the rate fixes the length, so send the same weeks of both beside it.",IF(C6&lt;&gt;C5,"Refuse the comparison: "&amp;C6&amp;" weeks against "&amp;C5&amp;" reads as "&amp;TEXT(ABS(B15),"0.0")&amp;" percent; compare the same weeks of both, with a rate per week beside them.","Revenue "&amp;IF(B15&lt;0,"fell ","rose ")&amp;TEXT(ABS(B15),"0.0")&amp;" percent"&amp;" on matched weeks."))))</f>
+        <f>IF(ABS(B10*C6-B6)&gt;=1,"Fix the weekly rate that divides by the wrong weeks before comparing anything.",IF(B13="closed quarters",IF(C7=C5,"Revenue "&amp;IF(B14&lt;0,"fell ","rose ")&amp;TEXT(ABS(B14),"0.0")&amp;" percent"&amp;" between closed quarters of "&amp;C5&amp;" weeks each.","The closed quarters cover different weeks: compare a rate per week."),IF(B13="rate per week","Per week, revenue "&amp;IF(B16&lt;0,"fell ","rose ")&amp;TEXT(ABS(B16),"0.0")&amp;" percent"&amp;" on the cut window; the rate fixes the length, so send the same weeks of both beside it.",IF(C6&lt;&gt;C5,"Refuse the comparison: "&amp;C6&amp;" weeks against "&amp;C5&amp;" reads as "&amp;TEXT(ABS(B15),"0.0")&amp;" percent; now that Q2 has closed, choose closed quarters, and while a quarter is open compare the same weeks of both with a rate per week beside them.","Revenue "&amp;IF(B15&lt;0,"fell ","rose ")&amp;TEXT(ABS(B15),"0.0")&amp;" percent"&amp;" on matched weeks."))))</f>
         <v/>
       </c>
     </row>
